--- a/data/replies/meridian/Meridian_Offer_RFX-0147.xlsx
+++ b/data/replies/meridian/Meridian_Offer_RFX-0147.xlsx
@@ -620,7 +620,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>All inks are water-based flexo inks compliant with EuPIA GMP and IS 15495; adhesives are starch based. MSDS available on request.</t>
+          <t>All inks are water-based flexo inks compliant with EuPIA GMP and IS 15495. MSDS available on request.</t>
         </is>
       </c>
     </row>
